--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-education-level.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="206">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,11 +387,13 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Liste des diplômes et qualifications.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -401,21 +403,6 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:qualification.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Liste des diplômes et qualifications.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
-  </si>
-  <si>
     <t>Extension.extension:qualificationType</t>
   </si>
   <si>
@@ -440,9 +427,6 @@
     <t>Extension.extension:qualificationType.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:qualificationType.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
     <t>Liste des types de diplômes.</t>
   </si>
   <si>
@@ -473,9 +457,6 @@
     <t>Extension.extension:academicDegree.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:academicDegree.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
     <t>Natures du cycle de formation des professionnels du RASS.</t>
   </si>
   <si>
@@ -506,9 +487,6 @@
     <t>Extension.extension:achievedLevel.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:achievedLevel.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
     <t>Liste des niveaux de formation</t>
   </si>
   <si>
@@ -537,9 +515,6 @@
   </si>
   <si>
     <t>Extension.extension:academicYear.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:academicYear.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>Listes des années universitaires.</t>
@@ -573,25 +548,19 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod</t>
-  </si>
-  <si>
-    <t>valuePeriod</t>
-  </si>
-  <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.id</t>
+    <t>Extension.extension:period.value[x].id</t>
   </si>
   <si>
     <t>Extension.extension.value[x].id</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.extension</t>
+    <t>Extension.extension:period.value[x].extension</t>
   </si>
   <si>
     <t>Extension.extension.value[x].extension</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.start</t>
+    <t>Extension.extension:period.value[x].start</t>
   </si>
   <si>
     <t>Extension.extension.value[x].start</t>
@@ -623,7 +592,7 @@
     <t>./low</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.end</t>
+    <t>Extension.extension:period.value[x].end</t>
   </si>
   <si>
     <t>Extension.extension.value[x].end</t>
@@ -671,7 +640,7 @@
     <t>Extension.extension:issuer.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|http://interopsante.org/fhir/StructureDefinition/FrOrganization)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|http://interopsante.org/fhir/StructureDefinition/FrOrganization)
 </t>
   </si>
   <si>
@@ -978,12 +947,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK51"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.91015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.53125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.25390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.80859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1922,29 +1891,31 @@
         <v>74</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1956,7 +1927,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>99</v>
@@ -1964,13 +1935,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
@@ -1992,15 +1963,17 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -2025,13 +1998,13 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -2049,22 +2022,22 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -2072,11 +2045,9 @@
         <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2097,17 +2068,15 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2156,30 +2125,30 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2190,7 +2159,7 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2202,13 +2171,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2247,42 +2216,42 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2290,10 +2259,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2305,22 +2274,24 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2350,42 +2321,42 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2393,7 +2364,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>82</v>
@@ -2408,24 +2379,22 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>74</v>
@@ -2443,13 +2412,13 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2467,19 +2436,19 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>99</v>
@@ -2487,12 +2456,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2513,15 +2484,17 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>74</v>
@@ -2558,44 +2531,44 @@
         <v>74</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
@@ -2616,13 +2589,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2649,13 +2622,13 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2673,7 +2646,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2682,13 +2655,13 @@
         <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -2696,11 +2669,9 @@
         <v>141</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
@@ -2709,7 +2680,7 @@
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2724,14 +2695,12 @@
         <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -2768,16 +2737,16 @@
         <v>74</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>97</v>
@@ -2800,10 +2769,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2811,7 +2780,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>82</v>
@@ -2826,22 +2795,24 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>74</v>
@@ -2883,10 +2854,10 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>82</v>
@@ -2898,15 +2869,15 @@
         <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2917,7 +2888,7 @@
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2929,13 +2900,13 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2962,62 +2933,64 @@
         <v>74</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>82</v>
@@ -3032,16 +3005,16 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3049,7 +3022,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>74</v>
@@ -3091,30 +3064,30 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3137,13 +3110,13 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3182,17 +3155,19 @@
         <v>74</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3201,25 +3176,23 @@
         <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
@@ -3228,7 +3201,7 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3240,13 +3213,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3273,46 +3246,46 @@
         <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
@@ -3320,17 +3293,15 @@
         <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>82</v>
@@ -3345,16 +3316,16 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3362,7 +3333,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3404,30 +3375,30 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3450,13 +3421,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3483,13 +3454,13 @@
         <v>74</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>74</v>
@@ -3507,7 +3478,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3516,23 +3487,25 @@
         <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="B25" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
@@ -3541,7 +3514,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3556,12 +3529,14 @@
         <v>90</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>28</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N25" s="2"/>
+      <c r="N25" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
@@ -3598,16 +3573,16 @@
         <v>74</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>97</v>
@@ -3630,10 +3605,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3641,7 +3616,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>82</v>
@@ -3656,24 +3631,22 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -3715,10 +3688,10 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>82</v>
@@ -3730,15 +3703,15 @@
         <v>74</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3749,7 +3722,7 @@
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
@@ -3761,13 +3734,13 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3806,50 +3779,50 @@
         <v>74</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>82</v>
@@ -3864,22 +3837,24 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>74</v>
@@ -3897,13 +3872,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3921,19 +3896,19 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>99</v>
@@ -3944,11 +3919,9 @@
         <v>163</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
@@ -3969,17 +3942,15 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>74</v>
@@ -4004,13 +3975,13 @@
         <v>74</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>74</v>
@@ -4028,32 +3999,34 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="B30" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
@@ -4074,13 +4047,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4131,30 +4104,30 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4165,7 +4138,7 @@
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>74</v>
@@ -4177,13 +4150,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4222,42 +4195,42 @@
         <v>74</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4265,10 +4238,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -4280,24 +4253,22 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4327,42 +4298,42 @@
         <v>74</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4370,7 +4341,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>82</v>
@@ -4385,22 +4356,24 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>74</v>
@@ -4430,29 +4403,31 @@
         <v>74</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>99</v>
@@ -4460,14 +4435,12 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="C34" t="s" s="2">
-        <v>126</v>
-      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4488,7 +4461,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>119</v>
@@ -4521,13 +4494,13 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -4545,7 +4518,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -4557,7 +4530,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>99</v>
@@ -4568,11 +4541,9 @@
         <v>174</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s" s="2">
         <v>175</v>
       </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
@@ -4593,13 +4564,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4650,41 +4621,41 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4696,15 +4667,17 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>74</v>
@@ -4741,34 +4714,34 @@
         <v>74</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
@@ -4776,7 +4749,7 @@
         <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4787,7 +4760,7 @@
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -4796,18 +4769,20 @@
         <v>74</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -4844,42 +4819,42 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>74</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4887,7 +4862,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>82</v>
@@ -4899,27 +4874,29 @@
         <v>74</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q38" s="2"/>
+      <c r="Q38" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="R38" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>74</v>
@@ -4961,32 +4938,34 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>99</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
@@ -5007,15 +4986,17 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>181</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>119</v>
+        <v>198</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5052,44 +5033,44 @@
         <v>74</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5110,13 +5091,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5167,7 +5148,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5176,21 +5157,21 @@
         <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5201,7 +5182,7 @@
         <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>74</v>
@@ -5213,13 +5194,13 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5258,53 +5239,53 @@
         <v>74</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
@@ -5316,16 +5297,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5333,7 +5314,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>74</v>
+        <v>197</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>74</v>
@@ -5363,31 +5344,31 @@
         <v>74</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>99</v>
@@ -5395,10 +5376,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5418,20 +5399,18 @@
         <v>74</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>74</v>
@@ -5480,7 +5459,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -5489,21 +5468,21 @@
         <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>197</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5511,7 +5490,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>82</v>
@@ -5523,29 +5502,27 @@
         <v>74</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q44" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>74</v>
@@ -5587,34 +5564,32 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>204</v>
+        <v>115</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>205</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>206</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
@@ -5623,7 +5598,7 @@
         <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5635,17 +5610,15 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>208</v>
+        <v>119</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>74</v>
@@ -5694,643 +5667,21 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK51" t="s" s="2">
         <v>99</v>
       </c>
     </row>
